--- a/research/traditional_assets/database/data/netherlands/netherlands_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,112 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.338</v>
-      </c>
-      <c r="E2">
-        <v>0.319</v>
+        <v>-0.346</v>
       </c>
       <c r="G2">
-        <v>0.429718875502008</v>
+        <v>0.9196613894428392</v>
       </c>
       <c r="H2">
-        <v>0.429718875502008</v>
+        <v>0.9132717431117985</v>
       </c>
       <c r="I2">
-        <v>0.9115430863207301</v>
+        <v>0.6964836580611852</v>
       </c>
       <c r="J2">
-        <v>0.9115430863207301</v>
+        <v>0.6964836580611852</v>
       </c>
       <c r="K2">
-        <v>22.9</v>
+        <v>-5.050000000000001</v>
       </c>
       <c r="L2">
-        <v>0.9196787148594378</v>
+        <v>-0.2055268405844288</v>
       </c>
       <c r="M2">
-        <v>1.8487</v>
+        <v>1.84059</v>
       </c>
       <c r="N2">
-        <v>0.02578382147838215</v>
+        <v>0.001990128235624851</v>
       </c>
       <c r="O2">
-        <v>0.0807292576419214</v>
+        <v>-0.3644732673267326</v>
       </c>
       <c r="P2">
-        <v>1.8487</v>
+        <v>1.83359</v>
       </c>
       <c r="Q2">
-        <v>0.02578382147838215</v>
+        <v>0.001982559522522328</v>
       </c>
       <c r="R2">
-        <v>0.0807292576419214</v>
+        <v>-0.3630871287128712</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.003803128344715553</v>
       </c>
       <c r="U2">
-        <v>0.792</v>
+        <v>469.6249999999999</v>
       </c>
       <c r="V2">
-        <v>0.01104602510460251</v>
+        <v>0.5077795558246653</v>
       </c>
       <c r="W2">
-        <v>0.2966321243523315</v>
+        <v>-1.703349282296651</v>
       </c>
       <c r="X2">
-        <v>0.04847570104366007</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="Y2">
-        <v>0.2481564233086715</v>
+        <v>-1.775803501337356</v>
       </c>
       <c r="Z2">
-        <v>0.3134327229425706</v>
-      </c>
-      <c r="AA2">
-        <v>0.2857074316249811</v>
+        <v>0.2145564093608103</v>
       </c>
       <c r="AB2">
-        <v>0.04303202276946833</v>
-      </c>
-      <c r="AC2">
-        <v>0.2426754088555128</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AD2">
-        <v>14.6</v>
+        <v>18.773</v>
       </c>
       <c r="AE2">
-        <v>0.6928857530690962</v>
+        <v>0.008500188893086513</v>
       </c>
       <c r="AF2">
-        <v>15.2928857530691</v>
+        <v>18.78150018889309</v>
       </c>
       <c r="AG2">
-        <v>14.5008857530691</v>
+        <v>-450.8434998111069</v>
       </c>
       <c r="AH2">
-        <v>0.1757946712617194</v>
+        <v>0.01990321555922827</v>
       </c>
       <c r="AI2">
-        <v>0.1288441649728249</v>
+        <v>0.1490317294849137</v>
       </c>
       <c r="AJ2">
-        <v>0.1682220040593122</v>
+        <v>-0.951113515313176</v>
       </c>
       <c r="AK2">
-        <v>0.1229921697402652</v>
+        <v>1.312111559637998</v>
       </c>
       <c r="AL2">
-        <v>0.089</v>
+        <v>13.943</v>
       </c>
       <c r="AM2">
-        <v>0.02099999999999999</v>
+        <v>13.17</v>
       </c>
       <c r="AN2">
-        <v>107.3529411764706</v>
+        <v>0.8230523039151213</v>
       </c>
       <c r="AO2">
-        <v>255.0561797752809</v>
+        <v>1.226852183891559</v>
       </c>
       <c r="AP2">
-        <v>106.6241599490375</v>
+        <v>-19.76603532864689</v>
       </c>
       <c r="AQ2">
-        <v>1080.952380952381</v>
+        <v>1.298861047835991</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +713,43 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.338</v>
-      </c>
-      <c r="E3">
-        <v>0.319</v>
+        <v>-0.346</v>
       </c>
       <c r="G3">
-        <v>0.429718875502008</v>
+        <v>0.907563025210084</v>
       </c>
       <c r="H3">
-        <v>0.429718875502008</v>
+        <v>0.907563025210084</v>
       </c>
       <c r="I3">
-        <v>0.9115430863207301</v>
+        <v>0.9033613445378151</v>
       </c>
       <c r="J3">
-        <v>0.9115430863207301</v>
+        <v>0.9033613445378151</v>
       </c>
       <c r="K3">
-        <v>22.9</v>
+        <v>21</v>
       </c>
       <c r="L3">
-        <v>0.9196787148594378</v>
+        <v>0.8823529411764706</v>
       </c>
       <c r="M3">
-        <v>1.8487</v>
+        <v>1.61155</v>
       </c>
       <c r="N3">
-        <v>0.02578382147838215</v>
+        <v>0.03191188118811882</v>
       </c>
       <c r="O3">
-        <v>0.0807292576419214</v>
+        <v>0.07674047619047619</v>
       </c>
       <c r="P3">
-        <v>1.8487</v>
+        <v>1.61155</v>
       </c>
       <c r="Q3">
-        <v>0.02578382147838215</v>
+        <v>0.03191188118811882</v>
       </c>
       <c r="R3">
-        <v>0.0807292576419214</v>
+        <v>0.07674047619047619</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +758,682 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.792</v>
+        <v>0.434</v>
       </c>
       <c r="V3">
-        <v>0.01104602510460251</v>
+        <v>0.008594059405940595</v>
       </c>
       <c r="W3">
-        <v>0.2966321243523315</v>
+        <v>0.231023102310231</v>
       </c>
       <c r="X3">
-        <v>0.04847570104366007</v>
+        <v>0.08090989155619538</v>
       </c>
       <c r="Y3">
-        <v>0.2481564233086715</v>
+        <v>0.1501132107540356</v>
       </c>
       <c r="Z3">
-        <v>0.3134327229425706</v>
+        <v>0.2494758909853249</v>
       </c>
       <c r="AA3">
-        <v>0.2857074316249811</v>
+        <v>0.2253668763102725</v>
       </c>
       <c r="AB3">
-        <v>0.04303202276946833</v>
+        <v>0.06932102638443589</v>
       </c>
       <c r="AC3">
-        <v>0.2426754088555128</v>
+        <v>0.1560458499258366</v>
       </c>
       <c r="AD3">
-        <v>14.6</v>
+        <v>17.1</v>
       </c>
       <c r="AE3">
-        <v>0.6928857530690962</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>15.2928857530691</v>
+        <v>17.1</v>
       </c>
       <c r="AG3">
-        <v>14.5008857530691</v>
+        <v>16.666</v>
       </c>
       <c r="AH3">
-        <v>0.1757946712617194</v>
+        <v>0.2529585798816568</v>
       </c>
       <c r="AI3">
-        <v>0.1288441649728249</v>
+        <v>0.1352848101265823</v>
       </c>
       <c r="AJ3">
-        <v>0.1682220040593122</v>
+        <v>0.2481314951016884</v>
       </c>
       <c r="AK3">
-        <v>0.1229921697402652</v>
+        <v>0.1323055427655082</v>
       </c>
       <c r="AL3">
-        <v>0.089</v>
+        <v>0.555</v>
       </c>
       <c r="AM3">
-        <v>0.02099999999999999</v>
+        <v>0.548</v>
       </c>
       <c r="AN3">
-        <v>107.3529411764706</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="AO3">
-        <v>255.0561797752809</v>
+        <v>38.73873873873873</v>
       </c>
       <c r="AP3">
-        <v>106.6241599490375</v>
+        <v>0.7715740740740741</v>
       </c>
       <c r="AQ3">
-        <v>1080.952380952381</v>
+        <v>39.23357664233576</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Navstone SE (BST:NUQA)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>-0.546</v>
+      </c>
+      <c r="G4">
+        <v>5.010570824524313</v>
+      </c>
+      <c r="H4">
+        <v>5.010570824524313</v>
+      </c>
+      <c r="I4">
+        <v>5.87737843551797</v>
+      </c>
+      <c r="J4">
+        <v>5.87737843551797</v>
+      </c>
+      <c r="K4">
+        <v>1.21</v>
+      </c>
+      <c r="L4">
+        <v>2.558139534883721</v>
+      </c>
+      <c r="M4">
+        <v>0.22204</v>
+      </c>
+      <c r="N4">
+        <v>0.02872445019404915</v>
+      </c>
+      <c r="O4">
+        <v>0.1835041322314049</v>
+      </c>
+      <c r="P4">
+        <v>0.22204</v>
+      </c>
+      <c r="Q4">
+        <v>0.02872445019404915</v>
+      </c>
+      <c r="R4">
+        <v>0.1835041322314049</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>2.38</v>
+      </c>
+      <c r="V4">
+        <v>0.3078913324708926</v>
+      </c>
+      <c r="W4">
+        <v>0.06142131979695432</v>
+      </c>
+      <c r="X4">
+        <v>0.07765525437710936</v>
+      </c>
+      <c r="Y4">
+        <v>-0.01623393458015505</v>
+      </c>
+      <c r="Z4">
+        <v>0.02473849372384937</v>
+      </c>
+      <c r="AA4">
+        <v>0.145397489539749</v>
+      </c>
+      <c r="AB4">
+        <v>0.07179001845129072</v>
+      </c>
+      <c r="AC4">
+        <v>0.07360747108845823</v>
+      </c>
+      <c r="AD4">
+        <v>1.61</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>1.61</v>
+      </c>
+      <c r="AG4">
+        <v>-0.7699999999999998</v>
+      </c>
+      <c r="AH4">
+        <v>0.1723768736616703</v>
+      </c>
+      <c r="AI4">
+        <v>0.08337648886587262</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.1106321839080459</v>
+      </c>
+      <c r="AK4">
+        <v>-0.04548139397519196</v>
+      </c>
+      <c r="AL4">
+        <v>1.63</v>
+      </c>
+      <c r="AM4">
+        <v>1.63</v>
+      </c>
+      <c r="AN4">
+        <v>0.5770609318996416</v>
+      </c>
+      <c r="AO4">
+        <v>1.705521472392638</v>
+      </c>
+      <c r="AP4">
+        <v>-0.2759856630824372</v>
+      </c>
+      <c r="AQ4">
+        <v>1.705521472392638</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Blockmate Ventures Inc. (TSXV:MATE)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>-0.00023</v>
+      </c>
+      <c r="G5">
+        <v>-4.60738255033557</v>
+      </c>
+      <c r="H5">
+        <v>-5.134228187919463</v>
+      </c>
+      <c r="I5">
+        <v>-5.512416234156435</v>
+      </c>
+      <c r="J5">
+        <v>-5.512416234156435</v>
+      </c>
+      <c r="K5">
+        <v>-3.56</v>
+      </c>
+      <c r="L5">
+        <v>-11.94630872483222</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0.288</v>
+      </c>
+      <c r="V5">
+        <v>0.2165413533834586</v>
+      </c>
+      <c r="W5">
+        <v>-1.703349282296651</v>
+      </c>
+      <c r="X5">
+        <v>0.07379667167205606</v>
+      </c>
+      <c r="Y5">
+        <v>-1.777145953968707</v>
+      </c>
+      <c r="AB5">
+        <v>0.07225764132443487</v>
+      </c>
+      <c r="AD5">
+        <v>0.063</v>
+      </c>
+      <c r="AE5">
+        <v>0.008500188893086513</v>
+      </c>
+      <c r="AF5">
+        <v>0.07150018889308651</v>
+      </c>
+      <c r="AG5">
+        <v>-0.2164998111069135</v>
+      </c>
+      <c r="AH5">
+        <v>0.05101689565204968</v>
+      </c>
+      <c r="AI5">
+        <v>-4.333394390383516</v>
+      </c>
+      <c r="AJ5">
+        <v>-0.1944317686395119</v>
+      </c>
+      <c r="AK5">
+        <v>0.7110014627591931</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>-0.002</v>
+      </c>
+      <c r="AN5">
+        <v>-0.0398481973434535</v>
+      </c>
+      <c r="AP5">
+        <v>0.1369385269493444</v>
+      </c>
+      <c r="AQ5">
+        <v>824.9999999999999</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ESG Core Investments B.V. (ENXTAM:ESG)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K6">
+        <v>-2.16</v>
+      </c>
+      <c r="M6">
+        <v>-0</v>
+      </c>
+      <c r="N6">
+        <v>-0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>-0</v>
+      </c>
+      <c r="Q6">
+        <v>-0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>261.4</v>
+      </c>
+      <c r="V6">
+        <v>1.000382701875239</v>
+      </c>
+      <c r="X6">
+        <v>0.07245421904070486</v>
+      </c>
+      <c r="AB6">
+        <v>0.07245421904070486</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>-261.4</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>2614.000000000891</v>
+      </c>
+      <c r="AK6">
+        <v>1.012589579701724</v>
+      </c>
+      <c r="AL6">
+        <v>6.04</v>
+      </c>
+      <c r="AM6">
+        <v>6.04</v>
+      </c>
+      <c r="AO6">
+        <v>-0.15</v>
+      </c>
+      <c r="AQ6">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Climate Transition Capital Acquisition I B.V. (ENXTAM:CTCA1)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K7">
+        <v>-11.3</v>
+      </c>
+      <c r="M7">
+        <v>0.007</v>
+      </c>
+      <c r="N7">
+        <v>2.80561122244489e-05</v>
+      </c>
+      <c r="O7">
+        <v>-0.0006194690265486725</v>
+      </c>
+      <c r="P7">
+        <v>-0</v>
+      </c>
+      <c r="Q7">
+        <v>-0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0.007</v>
+      </c>
+      <c r="T7">
+        <v>1</v>
+      </c>
+      <c r="U7">
+        <v>201.1</v>
+      </c>
+      <c r="V7">
+        <v>0.8060120240480961</v>
+      </c>
+      <c r="X7">
+        <v>0.07245421904070486</v>
+      </c>
+      <c r="AB7">
+        <v>0.07245421904070486</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>-201.1</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>-0</v>
+      </c>
+      <c r="AJ7">
+        <v>-4.15495867768595</v>
+      </c>
+      <c r="AK7">
+        <v>0.9388422035480859</v>
+      </c>
+      <c r="AL7">
+        <v>5.48</v>
+      </c>
+      <c r="AM7">
+        <v>5.48</v>
+      </c>
+      <c r="AO7">
+        <v>-0.1675182481751825</v>
+      </c>
+      <c r="AQ7">
+        <v>-0.1675182481751825</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SPEAR Investments I B.V. (ENXTAM:SPR1)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K8">
+        <v>-11.1</v>
+      </c>
+      <c r="M8">
+        <v>-0</v>
+      </c>
+      <c r="N8">
+        <v>-0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>-0</v>
+      </c>
+      <c r="Q8">
+        <v>-0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>3.75</v>
+      </c>
+      <c r="V8">
+        <v>0.01985177342509264</v>
+      </c>
+      <c r="X8">
+        <v>0.07245421904070486</v>
+      </c>
+      <c r="AB8">
+        <v>0.07245421904070486</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>-3.75</v>
+      </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>-0</v>
+      </c>
+      <c r="AJ8">
+        <v>-0.02025384823116392</v>
+      </c>
+      <c r="AK8">
+        <v>0.4980079681274901</v>
+      </c>
+      <c r="AL8">
+        <v>0.238</v>
+      </c>
+      <c r="AM8">
+        <v>0.238</v>
+      </c>
+      <c r="AO8">
+        <v>-6.344537815126051</v>
+      </c>
+      <c r="AQ8">
+        <v>-6.344537815126051</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>European Biotech Acquisition Corp. (NasdaqCM:EBAC)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K9">
+        <v>0.86</v>
+      </c>
+      <c r="M9">
+        <v>-0</v>
+      </c>
+      <c r="N9">
+        <v>-0</v>
+      </c>
+      <c r="O9">
+        <v>-0</v>
+      </c>
+      <c r="P9">
+        <v>-0</v>
+      </c>
+      <c r="Q9">
+        <v>-0</v>
+      </c>
+      <c r="R9">
+        <v>-0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0.273</v>
+      </c>
+      <c r="V9">
+        <v>0.001648550724637681</v>
+      </c>
+      <c r="W9">
+        <v>-0.1378205128205128</v>
+      </c>
+      <c r="X9">
+        <v>0.07245421904070486</v>
+      </c>
+      <c r="Y9">
+        <v>-0.2102747318612176</v>
+      </c>
+      <c r="AB9">
+        <v>0.07245421904070486</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>-0.273</v>
+      </c>
+      <c r="AH9">
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>-0</v>
+      </c>
+      <c r="AJ9">
+        <v>-0.001651272931826018</v>
+      </c>
+      <c r="AK9">
+        <v>0.04324409947726914</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>-0.764</v>
+      </c>
+      <c r="AQ9">
+        <v>2.866492146596859</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/netherlands/netherlands_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ9"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,112 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.346</v>
+        <v>-0.472</v>
+      </c>
+      <c r="E2">
+        <v>-0.393</v>
       </c>
       <c r="G2">
-        <v>0.9196613894428392</v>
+        <v>-0.6920502092050208</v>
       </c>
       <c r="H2">
-        <v>0.9132717431117985</v>
+        <v>-0.6920502092050208</v>
       </c>
       <c r="I2">
-        <v>0.6964836580611852</v>
+        <v>0.3255230125523012</v>
       </c>
       <c r="J2">
-        <v>0.6964836580611852</v>
+        <v>0.3255230125523012</v>
       </c>
       <c r="K2">
-        <v>-5.050000000000001</v>
+        <v>1.408</v>
       </c>
       <c r="L2">
-        <v>-0.2055268405844288</v>
+        <v>0.2945606694560669</v>
       </c>
       <c r="M2">
-        <v>1.84059</v>
+        <v>1.8321</v>
       </c>
       <c r="N2">
-        <v>0.001990128235624851</v>
+        <v>0.0277003326277593</v>
       </c>
       <c r="O2">
-        <v>-0.3644732673267326</v>
+        <v>1.301207386363637</v>
       </c>
       <c r="P2">
-        <v>1.83359</v>
+        <v>1.8321</v>
       </c>
       <c r="Q2">
-        <v>0.001982559522522328</v>
+        <v>0.0277003326277593</v>
       </c>
       <c r="R2">
-        <v>-0.3630871287128712</v>
+        <v>1.301207386363637</v>
       </c>
       <c r="S2">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.003803128344715553</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>469.6249999999999</v>
+        <v>2.4</v>
       </c>
       <c r="V2">
-        <v>0.5077795558246653</v>
+        <v>0.03628666465074085</v>
       </c>
       <c r="W2">
-        <v>-1.703349282296651</v>
+        <v>-0.003236127755901768</v>
       </c>
       <c r="X2">
-        <v>0.07245421904070486</v>
+        <v>0.06388601803675545</v>
       </c>
       <c r="Y2">
-        <v>-1.775803501337356</v>
+        <v>-0.06712214579265721</v>
       </c>
       <c r="Z2">
-        <v>0.2145564093608103</v>
+        <v>0.0396144634229217</v>
+      </c>
+      <c r="AA2">
+        <v>0.004929840296236473</v>
       </c>
       <c r="AB2">
-        <v>0.07245421904070486</v>
+        <v>0.06143195401724882</v>
+      </c>
+      <c r="AC2">
+        <v>-0.05650211372101234</v>
       </c>
       <c r="AD2">
-        <v>18.773</v>
+        <v>10.6</v>
       </c>
       <c r="AE2">
-        <v>0.008500188893086513</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>18.78150018889309</v>
+        <v>10.6</v>
       </c>
       <c r="AG2">
-        <v>-450.8434998111069</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.01990321555922827</v>
+        <v>0.1381287464164712</v>
       </c>
       <c r="AI2">
-        <v>0.1490317294849137</v>
+        <v>0.08242612752721618</v>
       </c>
       <c r="AJ2">
-        <v>-0.951113515313176</v>
+        <v>0.1103040086090933</v>
       </c>
       <c r="AK2">
-        <v>1.312111559637998</v>
+        <v>0.06497622820919176</v>
       </c>
       <c r="AL2">
-        <v>13.943</v>
+        <v>1.58</v>
       </c>
       <c r="AM2">
-        <v>13.17</v>
+        <v>1.58</v>
       </c>
       <c r="AN2">
-        <v>0.8230523039151213</v>
+        <v>5.915178571428571</v>
       </c>
       <c r="AO2">
-        <v>1.226852183891559</v>
+        <v>0.9848101265822783</v>
       </c>
       <c r="AP2">
-        <v>-19.76603532864689</v>
+        <v>4.575892857142857</v>
       </c>
       <c r="AQ2">
-        <v>1.298861047835991</v>
+        <v>0.9848101265822783</v>
       </c>
     </row>
     <row r="3">
@@ -712,44 +721,44 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D3">
-        <v>-0.346</v>
+      <c r="E3">
+        <v>-0.393</v>
       </c>
       <c r="G3">
-        <v>0.907563025210084</v>
+        <v>-0.7480106100795756</v>
       </c>
       <c r="H3">
-        <v>0.907563025210084</v>
+        <v>-0.7480106100795756</v>
       </c>
       <c r="I3">
-        <v>0.9033613445378151</v>
+        <v>0.4403183023872679</v>
       </c>
       <c r="J3">
-        <v>0.9033613445378151</v>
+        <v>0.4403183023872679</v>
       </c>
       <c r="K3">
-        <v>21</v>
+        <v>1.9</v>
       </c>
       <c r="L3">
-        <v>0.8823529411764706</v>
+        <v>0.5039787798408488</v>
       </c>
       <c r="M3">
-        <v>1.61155</v>
+        <v>1.8321</v>
       </c>
       <c r="N3">
-        <v>0.03191188118811882</v>
+        <v>0.03126450511945393</v>
       </c>
       <c r="O3">
-        <v>0.07674047619047619</v>
+        <v>0.964263157894737</v>
       </c>
       <c r="P3">
-        <v>1.61155</v>
+        <v>1.8321</v>
       </c>
       <c r="Q3">
-        <v>0.03191188118811882</v>
+        <v>0.03126450511945393</v>
       </c>
       <c r="R3">
-        <v>0.07674047619047619</v>
+        <v>0.964263157894737</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,73 +767,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.434</v>
+        <v>2.32</v>
       </c>
       <c r="V3">
-        <v>0.008594059405940595</v>
+        <v>0.03959044368600682</v>
       </c>
       <c r="W3">
-        <v>0.231023102310231</v>
+        <v>0.02132435465768799</v>
       </c>
       <c r="X3">
-        <v>0.08090989155619538</v>
+        <v>0.06546364753770927</v>
       </c>
       <c r="Y3">
-        <v>0.1501132107540356</v>
+        <v>-0.04413929288002127</v>
       </c>
       <c r="Z3">
-        <v>0.2494758909853249</v>
+        <v>0.0363433044450657</v>
       </c>
       <c r="AA3">
-        <v>0.2253668763102725</v>
+        <v>0.01600262211639498</v>
       </c>
       <c r="AB3">
-        <v>0.06932102638443589</v>
+        <v>0.060555519498696</v>
       </c>
       <c r="AC3">
-        <v>0.1560458499258366</v>
+        <v>-0.04455289738230103</v>
       </c>
       <c r="AD3">
-        <v>17.1</v>
+        <v>10.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>17.1</v>
+        <v>10.6</v>
       </c>
       <c r="AG3">
-        <v>16.666</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.2529585798816568</v>
+        <v>0.1531791907514451</v>
       </c>
       <c r="AI3">
-        <v>0.1352848101265823</v>
+        <v>0.09532374100719425</v>
       </c>
       <c r="AJ3">
-        <v>0.2481314951016884</v>
+        <v>0.1238038277511962</v>
       </c>
       <c r="AK3">
-        <v>0.1323055427655082</v>
+        <v>0.07604702424687729</v>
       </c>
       <c r="AL3">
-        <v>0.555</v>
+        <v>0.38</v>
       </c>
       <c r="AM3">
-        <v>0.548</v>
+        <v>0.38</v>
       </c>
       <c r="AN3">
-        <v>0.7916666666666666</v>
+        <v>6.127167630057803</v>
       </c>
       <c r="AO3">
-        <v>38.73873873873873</v>
+        <v>4.368421052631579</v>
       </c>
       <c r="AP3">
-        <v>0.7715740740740741</v>
+        <v>4.786127167630058</v>
       </c>
       <c r="AQ3">
-        <v>39.23357664233576</v>
+        <v>4.368421052631579</v>
       </c>
     </row>
     <row r="4">
@@ -835,7 +844,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Navstone SE (BST:NUQA)</t>
+          <t>Navstone SE (DB:NUQA)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -844,596 +853,115 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.546</v>
+        <v>-0.472</v>
       </c>
       <c r="G4">
-        <v>5.010570824524313</v>
+        <v>-0.4831683168316832</v>
       </c>
       <c r="H4">
-        <v>5.010570824524313</v>
+        <v>-0.4831683168316832</v>
       </c>
       <c r="I4">
-        <v>5.87737843551797</v>
+        <v>-0.102970297029703</v>
       </c>
       <c r="J4">
-        <v>5.87737843551797</v>
+        <v>-0.102970297029703</v>
       </c>
       <c r="K4">
-        <v>1.21</v>
+        <v>-0.492</v>
       </c>
       <c r="L4">
-        <v>2.558139534883721</v>
+        <v>-0.4871287128712871</v>
       </c>
       <c r="M4">
-        <v>0.22204</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.02872445019404915</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.1835041322314049</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>0.22204</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.02872445019404915</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.1835041322314049</v>
+        <v>0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>2.38</v>
+        <v>0.08</v>
       </c>
       <c r="V4">
-        <v>0.3078913324708926</v>
+        <v>0.01061007957559682</v>
       </c>
       <c r="W4">
-        <v>0.06142131979695432</v>
+        <v>-0.02779661016949153</v>
       </c>
       <c r="X4">
-        <v>0.07765525437710936</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="Y4">
-        <v>-0.01623393458015505</v>
+        <v>-0.09010499870529316</v>
       </c>
       <c r="Z4">
-        <v>0.02473849372384937</v>
+        <v>0.05965741287655051</v>
       </c>
       <c r="AA4">
-        <v>0.145397489539749</v>
+        <v>-0.006142941523922031</v>
       </c>
       <c r="AB4">
-        <v>0.07179001845129072</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AC4">
-        <v>0.07360747108845823</v>
+        <v>-0.06845133005972366</v>
       </c>
       <c r="AD4">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>-0.7699999999999998</v>
+        <v>-0.08</v>
       </c>
       <c r="AH4">
-        <v>0.1723768736616703</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>0.08337648886587262</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-0.1106321839080459</v>
+        <v>-0.01072386058981233</v>
       </c>
       <c r="AK4">
-        <v>-0.04548139397519196</v>
+        <v>-0.004618937644341801</v>
       </c>
       <c r="AL4">
-        <v>1.63</v>
+        <v>1.2</v>
       </c>
       <c r="AM4">
-        <v>1.63</v>
+        <v>1.2</v>
       </c>
       <c r="AN4">
-        <v>0.5770609318996416</v>
+        <v>0</v>
       </c>
       <c r="AO4">
-        <v>1.705521472392638</v>
+        <v>-0.08666666666666667</v>
       </c>
       <c r="AP4">
-        <v>-0.2759856630824372</v>
+        <v>-1.290322580645161</v>
       </c>
       <c r="AQ4">
-        <v>1.705521472392638</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Blockmate Ventures Inc. (TSXV:MATE)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>-0.00023</v>
-      </c>
-      <c r="G5">
-        <v>-4.60738255033557</v>
-      </c>
-      <c r="H5">
-        <v>-5.134228187919463</v>
-      </c>
-      <c r="I5">
-        <v>-5.512416234156435</v>
-      </c>
-      <c r="J5">
-        <v>-5.512416234156435</v>
-      </c>
-      <c r="K5">
-        <v>-3.56</v>
-      </c>
-      <c r="L5">
-        <v>-11.94630872483222</v>
-      </c>
-      <c r="M5">
-        <v>-0</v>
-      </c>
-      <c r="N5">
-        <v>-0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>-0</v>
-      </c>
-      <c r="Q5">
-        <v>-0</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>0.288</v>
-      </c>
-      <c r="V5">
-        <v>0.2165413533834586</v>
-      </c>
-      <c r="W5">
-        <v>-1.703349282296651</v>
-      </c>
-      <c r="X5">
-        <v>0.07379667167205606</v>
-      </c>
-      <c r="Y5">
-        <v>-1.777145953968707</v>
-      </c>
-      <c r="AB5">
-        <v>0.07225764132443487</v>
-      </c>
-      <c r="AD5">
-        <v>0.063</v>
-      </c>
-      <c r="AE5">
-        <v>0.008500188893086513</v>
-      </c>
-      <c r="AF5">
-        <v>0.07150018889308651</v>
-      </c>
-      <c r="AG5">
-        <v>-0.2164998111069135</v>
-      </c>
-      <c r="AH5">
-        <v>0.05101689565204968</v>
-      </c>
-      <c r="AI5">
-        <v>-4.333394390383516</v>
-      </c>
-      <c r="AJ5">
-        <v>-0.1944317686395119</v>
-      </c>
-      <c r="AK5">
-        <v>0.7110014627591931</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
-        <v>-0.002</v>
-      </c>
-      <c r="AN5">
-        <v>-0.0398481973434535</v>
-      </c>
-      <c r="AP5">
-        <v>0.1369385269493444</v>
-      </c>
-      <c r="AQ5">
-        <v>824.9999999999999</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ESG Core Investments B.V. (ENXTAM:ESG)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="K6">
-        <v>-2.16</v>
-      </c>
-      <c r="M6">
-        <v>-0</v>
-      </c>
-      <c r="N6">
-        <v>-0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>-0</v>
-      </c>
-      <c r="Q6">
-        <v>-0</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>261.4</v>
-      </c>
-      <c r="V6">
-        <v>1.000382701875239</v>
-      </c>
-      <c r="X6">
-        <v>0.07245421904070486</v>
-      </c>
-      <c r="AB6">
-        <v>0.07245421904070486</v>
-      </c>
-      <c r="AD6">
-        <v>0</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>0</v>
-      </c>
-      <c r="AG6">
-        <v>-261.4</v>
-      </c>
-      <c r="AH6">
-        <v>0</v>
-      </c>
-      <c r="AI6">
-        <v>0</v>
-      </c>
-      <c r="AJ6">
-        <v>2614.000000000891</v>
-      </c>
-      <c r="AK6">
-        <v>1.012589579701724</v>
-      </c>
-      <c r="AL6">
-        <v>6.04</v>
-      </c>
-      <c r="AM6">
-        <v>6.04</v>
-      </c>
-      <c r="AO6">
-        <v>-0.15</v>
-      </c>
-      <c r="AQ6">
-        <v>-0.15</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Climate Transition Capital Acquisition I B.V. (ENXTAM:CTCA1)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="K7">
-        <v>-11.3</v>
-      </c>
-      <c r="M7">
-        <v>0.007</v>
-      </c>
-      <c r="N7">
-        <v>2.80561122244489e-05</v>
-      </c>
-      <c r="O7">
-        <v>-0.0006194690265486725</v>
-      </c>
-      <c r="P7">
-        <v>-0</v>
-      </c>
-      <c r="Q7">
-        <v>-0</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0.007</v>
-      </c>
-      <c r="T7">
-        <v>1</v>
-      </c>
-      <c r="U7">
-        <v>201.1</v>
-      </c>
-      <c r="V7">
-        <v>0.8060120240480961</v>
-      </c>
-      <c r="X7">
-        <v>0.07245421904070486</v>
-      </c>
-      <c r="AB7">
-        <v>0.07245421904070486</v>
-      </c>
-      <c r="AD7">
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>0</v>
-      </c>
-      <c r="AG7">
-        <v>-201.1</v>
-      </c>
-      <c r="AH7">
-        <v>0</v>
-      </c>
-      <c r="AI7">
-        <v>-0</v>
-      </c>
-      <c r="AJ7">
-        <v>-4.15495867768595</v>
-      </c>
-      <c r="AK7">
-        <v>0.9388422035480859</v>
-      </c>
-      <c r="AL7">
-        <v>5.48</v>
-      </c>
-      <c r="AM7">
-        <v>5.48</v>
-      </c>
-      <c r="AO7">
-        <v>-0.1675182481751825</v>
-      </c>
-      <c r="AQ7">
-        <v>-0.1675182481751825</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>SPEAR Investments I B.V. (ENXTAM:SPR1)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="K8">
-        <v>-11.1</v>
-      </c>
-      <c r="M8">
-        <v>-0</v>
-      </c>
-      <c r="N8">
-        <v>-0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>-0</v>
-      </c>
-      <c r="Q8">
-        <v>-0</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>3.75</v>
-      </c>
-      <c r="V8">
-        <v>0.01985177342509264</v>
-      </c>
-      <c r="X8">
-        <v>0.07245421904070486</v>
-      </c>
-      <c r="AB8">
-        <v>0.07245421904070486</v>
-      </c>
-      <c r="AD8">
-        <v>0</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
-        <v>0</v>
-      </c>
-      <c r="AG8">
-        <v>-3.75</v>
-      </c>
-      <c r="AH8">
-        <v>0</v>
-      </c>
-      <c r="AI8">
-        <v>-0</v>
-      </c>
-      <c r="AJ8">
-        <v>-0.02025384823116392</v>
-      </c>
-      <c r="AK8">
-        <v>0.4980079681274901</v>
-      </c>
-      <c r="AL8">
-        <v>0.238</v>
-      </c>
-      <c r="AM8">
-        <v>0.238</v>
-      </c>
-      <c r="AO8">
-        <v>-6.344537815126051</v>
-      </c>
-      <c r="AQ8">
-        <v>-6.344537815126051</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>European Biotech Acquisition Corp. (NasdaqCM:EBAC)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="K9">
-        <v>0.86</v>
-      </c>
-      <c r="M9">
-        <v>-0</v>
-      </c>
-      <c r="N9">
-        <v>-0</v>
-      </c>
-      <c r="O9">
-        <v>-0</v>
-      </c>
-      <c r="P9">
-        <v>-0</v>
-      </c>
-      <c r="Q9">
-        <v>-0</v>
-      </c>
-      <c r="R9">
-        <v>-0</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>0.273</v>
-      </c>
-      <c r="V9">
-        <v>0.001648550724637681</v>
-      </c>
-      <c r="W9">
-        <v>-0.1378205128205128</v>
-      </c>
-      <c r="X9">
-        <v>0.07245421904070486</v>
-      </c>
-      <c r="Y9">
-        <v>-0.2102747318612176</v>
-      </c>
-      <c r="AB9">
-        <v>0.07245421904070486</v>
-      </c>
-      <c r="AD9">
-        <v>0</v>
-      </c>
-      <c r="AE9">
-        <v>0</v>
-      </c>
-      <c r="AF9">
-        <v>0</v>
-      </c>
-      <c r="AG9">
-        <v>-0.273</v>
-      </c>
-      <c r="AH9">
-        <v>0</v>
-      </c>
-      <c r="AI9">
-        <v>-0</v>
-      </c>
-      <c r="AJ9">
-        <v>-0.001651272931826018</v>
-      </c>
-      <c r="AK9">
-        <v>0.04324409947726914</v>
-      </c>
-      <c r="AL9">
-        <v>0</v>
-      </c>
-      <c r="AM9">
-        <v>-0.764</v>
-      </c>
-      <c r="AQ9">
-        <v>2.866492146596859</v>
+        <v>-0.08666666666666667</v>
       </c>
     </row>
   </sheetData>
